--- a/results/BeamDial-results-v0.1.xlsx
+++ b/results/BeamDial-results-v0.1.xlsx
@@ -439,7 +439,7 @@
     <t xml:space="preserve">Grader fix: an earlier grading under-counted math (93.1%). This workbook uses the fixed grader (96.7% over all runs).</t>
   </si>
   <si>
-    <t xml:space="preserve">Code and data: github.com/OWNER/beamdial</t>
+    <t xml:space="preserve">Code: https://github.com/CoderRahul01/beamdial  Data: https://huggingface.co/datasets/PengoSword123/beamdial-v0.1</t>
   </si>
   <si>
     <t xml:space="preserve">Source</t>
